--- a/Samples/test/02_invalid_rows.xlsx
+++ b/Samples/test/02_invalid_rows.xlsx
@@ -3125,7 +3125,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BBBBBBBBBBBBBBBBBBBBBBBBBBBBBB</t>
+          <t>BBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBBB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
